--- a/Banco_de_Imoveis.xlsx
+++ b/Banco_de_Imoveis.xlsx
@@ -1,29 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28521"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/53359c59c4c07b84/Documentos/Python Scripts/Projeto Metis/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_F00C9D9E4E3C5E9C696E5F0A35096F3CFB1B55AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDD2B59B-83A2-4546-BAFE-F68F803A7B3E}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_1C2BDE6ED2E2DF45F482035DD7A9155A3020B93E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FB057AC-81E8-4085-BB8B-86785EA6EF0D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consultar" sheetId="1" r:id="rId1"/>
     <sheet name="Link de Imóveis" sheetId="2" r:id="rId2"/>
-    <sheet name="Log de Execução" sheetId="3" r:id="rId3"/>
-    <sheet name="Planilha1" sheetId="4" r:id="rId4"/>
+    <sheet name="Banco de Dados" sheetId="3" r:id="rId3"/>
+    <sheet name="Log de Execução" sheetId="4" r:id="rId4"/>
+    <sheet name="Planilha1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="48">
   <si>
     <t>CNPJ/CPF</t>
   </si>
@@ -43,6 +55,15 @@
     <t>CNPJ proprietário</t>
   </si>
   <si>
+    <t>08.958.952/0001-24</t>
+  </si>
+  <si>
+    <t>345.406.529-15</t>
+  </si>
+  <si>
+    <t>CPF proprietário</t>
+  </si>
+  <si>
     <t>Código do Imóvel</t>
   </si>
   <si>
@@ -52,7 +73,61 @@
     <t>URL do Imóvel</t>
   </si>
   <si>
+    <t>CPF/CNPJ</t>
+  </si>
+  <si>
+    <t>Ano</t>
+  </si>
+  <si>
+    <t>Descrição</t>
+  </si>
+  <si>
+    <t>Nº parc.</t>
+  </si>
+  <si>
+    <t>Sub. parc.</t>
+  </si>
+  <si>
+    <t>Tipo Débito</t>
+  </si>
+  <si>
+    <t>Dt. vcto.</t>
+  </si>
+  <si>
+    <t>Vlr. parcela</t>
+  </si>
+  <si>
+    <t>Desconto</t>
+  </si>
+  <si>
+    <t>Vlr. juros</t>
+  </si>
+  <si>
+    <t>Vlr. multa</t>
+  </si>
+  <si>
+    <t>Vlr. correção</t>
+  </si>
+  <si>
+    <t>Vlr. honorário</t>
+  </si>
+  <si>
+    <t>Vlr. corrigido</t>
+  </si>
+  <si>
+    <t>Pagamento</t>
+  </si>
+  <si>
+    <t>Ações</t>
+  </si>
+  <si>
     <t>Data/Hora</t>
+  </si>
+  <si>
+    <t>CNPJ</t>
+  </si>
+  <si>
+    <t>Tipo</t>
   </si>
   <si>
     <t>Evento</t>
@@ -117,7 +192,16 @@
     <t>2025-01-24 07:22:13</t>
   </si>
   <si>
-    <t>CPF proprietário</t>
+    <t>2025-01-26 18:44:12</t>
+  </si>
+  <si>
+    <t>Consulta realizada com sucesso.</t>
+  </si>
+  <si>
+    <t>2025-01-26 18:44:21</t>
+  </si>
+  <si>
+    <t>2025-01-26 18:44:38</t>
   </si>
   <si>
     <t>Cód. do imóvel</t>
@@ -130,7 +214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,10 +223,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF767676"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -450,35 +536,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -488,29 +590,34 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -521,127 +628,79 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="F1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="I1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="J1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
+      <c r="K1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -651,30 +710,217 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Banco_de_Imoveis.xlsx
+++ b/Banco_de_Imoveis.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28521"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_1C2BDE6ED2E2DF45F482035DD7A9155A3020B93E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FB057AC-81E8-4085-BB8B-86785EA6EF0D}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/53359c59c4c07b84/Documentos/Python Scripts/Projeto Metis/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_E6EA2F254200541DE2B219029F57F61F0C706E6A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CF17FE8-213E-4D7C-BC9D-FF73E3AEBEF4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consultar" sheetId="1" r:id="rId1"/>
@@ -14,28 +19,12 @@
     <sheet name="Log de Execução" sheetId="4" r:id="rId4"/>
     <sheet name="Planilha1" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="144">
   <si>
     <t>CNPJ/CPF</t>
   </si>
@@ -52,13 +41,25 @@
     <t>50.136.653/0001-70</t>
   </si>
   <si>
+    <t>Finalizado</t>
+  </si>
+  <si>
+    <t>2025-01-26 22:26:18</t>
+  </si>
+  <si>
     <t>CNPJ proprietário</t>
   </si>
   <si>
     <t>08.958.952/0001-24</t>
   </si>
   <si>
-    <t>345.406.529-15</t>
+    <t>2025-01-26 22:26:28</t>
+  </si>
+  <si>
+    <t>Erro: Elemento da tela 2 não encontrado. O login pode ter falhado.</t>
+  </si>
+  <si>
+    <t>2025-01-26 22:26:40</t>
   </si>
   <si>
     <t>CPF proprietário</t>
@@ -70,9 +71,327 @@
     <t>Inscrição Imobiliária</t>
   </si>
   <si>
+    <t>Logradouro</t>
+  </si>
+  <si>
+    <t>Complemento</t>
+  </si>
+  <si>
+    <t>Bairro</t>
+  </si>
+  <si>
+    <t>Situação</t>
+  </si>
+  <si>
     <t>URL do Imóvel</t>
   </si>
   <si>
+    <t>45044</t>
+  </si>
+  <si>
+    <t>001.03.082.5255.001</t>
+  </si>
+  <si>
+    <t>BRASILIA nº 1111</t>
+  </si>
+  <si>
+    <t>BARRACÃO PRINCIPAL</t>
+  </si>
+  <si>
+    <t>SAO CRISTOVAO</t>
+  </si>
+  <si>
+    <t>Ativo</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.03.082.5255.001</t>
+  </si>
+  <si>
+    <t>Em progresso</t>
+  </si>
+  <si>
+    <t>47762</t>
+  </si>
+  <si>
+    <t>001.03.082.5255.002</t>
+  </si>
+  <si>
+    <t>BARRACÃO LATERAL</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.03.082.5255.002</t>
+  </si>
+  <si>
+    <t>47763</t>
+  </si>
+  <si>
+    <t>001.03.082.5255.003</t>
+  </si>
+  <si>
+    <t>BARRACÃO FUNDOS</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.03.082.5255.003</t>
+  </si>
+  <si>
+    <t>47764</t>
+  </si>
+  <si>
+    <t>001.03.082.5255.004</t>
+  </si>
+  <si>
+    <t>BARRACÃO</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.03.082.5255.004</t>
+  </si>
+  <si>
+    <t>28569</t>
+  </si>
+  <si>
+    <t>001.01.012.0018.011</t>
+  </si>
+  <si>
+    <t>VICTOR BAPTISTA ADAMI nº 18</t>
+  </si>
+  <si>
+    <t>TATTO</t>
+  </si>
+  <si>
+    <t>CENTRO</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.012.0018.011</t>
+  </si>
+  <si>
+    <t>2025-01-26 22:26:27</t>
+  </si>
+  <si>
+    <t>28570</t>
+  </si>
+  <si>
+    <t>001.01.012.0018.012</t>
+  </si>
+  <si>
+    <t>SALA 32</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.012.0018.012</t>
+  </si>
+  <si>
+    <t>28571</t>
+  </si>
+  <si>
+    <t>001.01.012.0018.013</t>
+  </si>
+  <si>
+    <t>SALA 33</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.012.0018.013</t>
+  </si>
+  <si>
+    <t>28572</t>
+  </si>
+  <si>
+    <t>001.01.012.0018.014</t>
+  </si>
+  <si>
+    <t>SALA 34</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.012.0018.014</t>
+  </si>
+  <si>
+    <t>28577</t>
+  </si>
+  <si>
+    <t>001.01.012.0018.019</t>
+  </si>
+  <si>
+    <t>BOX 05</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.012.0018.019</t>
+  </si>
+  <si>
+    <t>28578</t>
+  </si>
+  <si>
+    <t>001.01.012.0018.020</t>
+  </si>
+  <si>
+    <t>BOX 06</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.012.0018.020</t>
+  </si>
+  <si>
+    <t>2779</t>
+  </si>
+  <si>
+    <t>001.01.061.0184.001</t>
+  </si>
+  <si>
+    <t>VICTOR BAPTISTA ADAMI nº 789</t>
+  </si>
+  <si>
+    <t>NOVA SISTEMAS</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.061.0184.001</t>
+  </si>
+  <si>
+    <t>2780</t>
+  </si>
+  <si>
+    <t>001.01.061.0184.002</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.061.0184.002</t>
+  </si>
+  <si>
+    <t>2781</t>
+  </si>
+  <si>
+    <t>001.01.061.0184.003</t>
+  </si>
+  <si>
+    <t>MALHARIA JULIAN</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.061.0184.003</t>
+  </si>
+  <si>
+    <t>36370</t>
+  </si>
+  <si>
+    <t>001.01.061.0184.004</t>
+  </si>
+  <si>
+    <t>JULIAN BORDADO</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.061.0184.004</t>
+  </si>
+  <si>
+    <t>2782</t>
+  </si>
+  <si>
+    <t>001.01.061.0184.005</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.061.0184.005</t>
+  </si>
+  <si>
+    <t>36371</t>
+  </si>
+  <si>
+    <t>001.01.061.0184.006</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.061.0184.006</t>
+  </si>
+  <si>
+    <t>36372</t>
+  </si>
+  <si>
+    <t>001.01.061.0184.007</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.061.0184.007</t>
+  </si>
+  <si>
+    <t>36373</t>
+  </si>
+  <si>
+    <t>001.01.061.0184.008</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.061.0184.008</t>
+  </si>
+  <si>
+    <t>36374</t>
+  </si>
+  <si>
+    <t>001.01.061.0184.009</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.061.0184.009</t>
+  </si>
+  <si>
+    <t>36375</t>
+  </si>
+  <si>
+    <t>001.01.061.0184.010</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.01.061.0184.010</t>
+  </si>
+  <si>
+    <t>6378</t>
+  </si>
+  <si>
+    <t>001.03.001.0575.002</t>
+  </si>
+  <si>
+    <t>SENADOR SALGADO FILHO nº 385</t>
+  </si>
+  <si>
+    <t>APTO. 1</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.03.001.0575.002</t>
+  </si>
+  <si>
+    <t>6379</t>
+  </si>
+  <si>
+    <t>001.03.001.0575.003</t>
+  </si>
+  <si>
+    <t>CASA FUNDOS</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.03.001.0575.003</t>
+  </si>
+  <si>
+    <t>6380</t>
+  </si>
+  <si>
+    <t>001.03.001.0575.004</t>
+  </si>
+  <si>
+    <t>APTO. 2</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.03.001.0575.004</t>
+  </si>
+  <si>
+    <t>6381</t>
+  </si>
+  <si>
+    <t>001.03.001.0575.005</t>
+  </si>
+  <si>
+    <t>SHALOM MODAS</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.03.001.0575.005</t>
+  </si>
+  <si>
+    <t>6382</t>
+  </si>
+  <si>
+    <t>001.03.001.0575.006</t>
+  </si>
+  <si>
+    <t>PARANA COMERCIAL</t>
+  </si>
+  <si>
+    <t>https://nfse1.publica.inf.br/cacador_eiptu/jsp/portal/home.jsp?action=seleciona_imovel&amp;nr=001.03.001.0575.006</t>
+  </si>
+  <si>
     <t>CPF/CNPJ</t>
   </si>
   <si>
@@ -131,77 +450,6 @@
   </si>
   <si>
     <t>Evento</t>
-  </si>
-  <si>
-    <t>2025-01-24 07:10:34</t>
-  </si>
-  <si>
-    <t>Erro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erro ao coletar links: Message: no such element: Unable to locate element: {"method":"tag name","selector":"a"}
-  (Session info: MicrosoftEdge=132.0.2957.115); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
-Stacktrace:
-	GetHandleVerifier [0x00007FF64CD60AD5+13637]
-	Microsoft::Applications::Events::EventProperty::empty [0x00007FF64CFEBC04+2078900]
-	Microsoft::Applications::Events::EventProperty::empty [0x00007FF64CF466C6+1401718]
-	(No symbol) [0x00007FF64CB1D84C]
-	(No symbol) [0x00007FF64CB1DA0B]
-	(No symbol) [0x00007FF64CB13E0C]
-	(No symbol) [0x00007FF64CB3DE1F]
-	(No symbol) [0x00007FF64CB13DB7]
-	(No symbol) [0x00007FF64CB13C7D]
-	(No symbol) [0x00007FF64CB3E0C0]
-	(No symbol) [0x00007FF64CB13DB7]
-	(No symbol) [0x00007FF64CB5890D]
-	(No symbol) [0x00007FF64CB3DA43]
-	(No symbol) [0x00007FF64CB13304]
-	(No symbol) [0x00007FF64CB12636]
-	(No symbol) [0x00007FF64CB12EF1]
-	(No symbol) [0x00007FF64CB9E1A4]
-	(No symbol) [0x00007FF64CC4608F]
-	(No symbol) [0x00007FF64CBA1B93]
-	Microsoft::Applications::Events::EventProperty::to_string [0x00007FF64D0A81F9+269801]
-	Microsoft::Applications::Events::ILogConfiguration::operator* [0x00007FF64CCF7191+519345]
-	Microsoft::Applications::Events::ILogConfiguration::operator* [0x00007FF64CCF2484+499620]
-	Microsoft::Applications::Events::ILogConfiguration::operator* [0x00007FF64CCF25C9+499945]
-	Microsoft::Applications::Events::ILogConfiguration::operator* [0x00007FF64CCE7546+454758]
-	BaseThreadInitThunk [0x00007FF8C332E8D7+23]
-	RtlUserThreadStart [0x00007FF8C4EFFBCC+44]
-</t>
-  </si>
-  <si>
-    <t>2025-01-24 07:17:03</t>
-  </si>
-  <si>
-    <t>2025-01-24 07:17:21</t>
-  </si>
-  <si>
-    <t>2025-01-24 07:18:54</t>
-  </si>
-  <si>
-    <t>Sucesso</t>
-  </si>
-  <si>
-    <t>Dados salvos em dados_50.136.653_0001-70.csv</t>
-  </si>
-  <si>
-    <t>2025-01-24 07:21:19</t>
-  </si>
-  <si>
-    <t>2025-01-24 07:22:13</t>
-  </si>
-  <si>
-    <t>2025-01-26 18:44:12</t>
-  </si>
-  <si>
-    <t>Consulta realizada com sucesso.</t>
-  </si>
-  <si>
-    <t>2025-01-26 18:44:21</t>
-  </si>
-  <si>
-    <t>2025-01-26 18:44:38</t>
   </si>
   <si>
     <t>Cód. do imóvel</t>
@@ -214,7 +462,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,6 +474,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -248,14 +504,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -536,16 +795,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,29 +818,56 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
       <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>6</v>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>34540652915</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
       <c r="D4" t="s">
-        <v>8</v>
-      </c>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -590,38 +876,838 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="105" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" t="s">
+        <v>97</v>
+      </c>
+      <c r="I20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" t="s">
+        <v>100</v>
+      </c>
+      <c r="I21" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>2</v>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" t="s">
+        <v>109</v>
+      </c>
+      <c r="I23" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" t="s">
+        <v>113</v>
+      </c>
+      <c r="I24" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" t="s">
+        <v>116</v>
+      </c>
+      <c r="F25" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" t="s">
+        <v>121</v>
+      </c>
+      <c r="I26" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{1CE9D050-08A0-4DD0-AE64-0FD2DBC80D0C}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -629,7 +1715,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
@@ -650,57 +1736,57 @@
     <col min="17" max="17" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="I1" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="J1" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="K1" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="L1" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="M1" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="N1" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="O1" t="s">
-        <v>25</v>
+        <v>135</v>
       </c>
       <c r="P1" t="s">
-        <v>26</v>
+        <v>136</v>
       </c>
       <c r="Q1" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -710,8 +1796,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
@@ -720,174 +1806,21 @@
     <col min="5" max="5" width="53.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -898,29 +1831,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
